--- a/src/utils/sxsyzlzq/friends/laowang/zz_lw_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/laowang/zz_lw_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10725" windowHeight="11385" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="13980" windowHeight="11415" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="6" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="70">
   <si>
     <t>名称</t>
   </si>
@@ -41,6 +41,9 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>愚笨鲸头鹅</t>
+  </si>
+  <si>
     <t>蓄力射手</t>
   </si>
   <si>
@@ -56,12 +59,12 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
+    <t>无畏猎户</t>
+  </si>
+  <si>
     <t>活力仙人掌</t>
   </si>
   <si>
-    <t>地洞巨獾</t>
-  </si>
-  <si>
     <t>圣兽祭师</t>
   </si>
   <si>
@@ -77,12 +80,12 @@
     <t>紫色卡等：</t>
   </si>
   <si>
+    <t>鸵鸟王·霍利</t>
+  </si>
+  <si>
     <t>旷野游侠·大羽</t>
   </si>
   <si>
-    <t>鸵鸟王·霍利</t>
-  </si>
-  <si>
     <t>比尔&amp;比利</t>
   </si>
   <si>
@@ -101,10 +104,10 @@
     <t>蛮石卡等：</t>
   </si>
   <si>
-    <t>疯狂战意</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
+    <t>无面狂奔者</t>
+  </si>
+  <si>
+    <t>腐化甲蛾</t>
   </si>
   <si>
     <t>碎颅魔</t>
@@ -116,7 +119,13 @@
     <t>铸甲熔岩魔</t>
   </si>
   <si>
-    <t>嗜血破面</t>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>破卵而出</t>
   </si>
   <si>
     <t>灼神双炎</t>
@@ -149,6 +158,9 @@
     <t>炼狱卡等：</t>
   </si>
   <si>
+    <t>长耳庄巧姑</t>
+  </si>
+  <si>
     <t>太极剑法</t>
   </si>
   <si>
@@ -158,9 +170,6 @@
     <t>执剑道者</t>
   </si>
   <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
     <t>连击</t>
   </si>
   <si>
@@ -194,12 +203,18 @@
     <t>洞悉之眼</t>
   </si>
   <si>
+    <t>电流激活</t>
+  </si>
+  <si>
     <t>方尖魔碑</t>
   </si>
   <si>
     <t>沉重否定</t>
   </si>
   <si>
+    <t>万圣节草人</t>
+  </si>
+  <si>
     <t>全数否定</t>
   </si>
   <si>
@@ -216,9 +231,6 @@
   </si>
   <si>
     <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>改造魔卷</t>
   </si>
   <si>
     <t>米拉方舟</t>
@@ -1215,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
         <v>22</v>
@@ -1237,55 +1249,55 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C4" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>19.3333333333333</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2">
-        <v>20</v>
-      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>21.25</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1296,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1304,26 +1316,26 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1334,13 +1346,13 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1355,19 +1367,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="2">
-        <f>AVERAGE(C10:C16)</f>
-        <v>20.1428571428571</v>
+        <f>AVERAGE(C11:C16)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="3">
         <v>3</v>
@@ -1378,18 +1390,18 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -1400,7 +1412,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
@@ -1411,7 +1423,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
         <v>7</v>
@@ -1432,26 +1444,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C22:C26)</f>
-        <v>18</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
-        <v>19.2666666666667</v>
+        <f>AVERAGE(C2:C5,C11:C16,C22:C26)</f>
+        <v>20.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1475,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1484,24 +1496,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1516,20 +1528,20 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <f>AVERAGE(C2:C3)</f>
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -1540,7 +1552,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -1551,7 +1563,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
@@ -1562,10 +1574,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2">
         <v>19</v>
@@ -1573,157 +1585,179 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2">
         <v>6</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C18" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C9:C16)</f>
-        <v>20.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2</v>
-      </c>
-      <c r="C22" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>20</v>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C9:C18)</f>
+        <v>19.5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3">
         <v>6</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C28" s="3">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C22:C26)</f>
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C3,C9:C16,C22:C26)</f>
-        <v>19.8666666666667</v>
+      <c r="C31" s="3">
+        <f>AVERAGE(C24:C28)</f>
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C3,C9:C18,C24:C28)</f>
+        <v>19.2352941176471</v>
       </c>
     </row>
   </sheetData>
@@ -1756,51 +1790,51 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1811,18 +1845,18 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1833,18 +1867,18 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -1855,24 +1889,24 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
       </c>
       <c r="C11" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
       </c>
       <c r="C12" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1887,31 +1921,31 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
-        <v>16.2727272727273</v>
+        <v>15.5454545454545</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -1922,7 +1956,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1943,19 +1977,19 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C18:C20)</f>
-        <v>18.6666666666667</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -1976,10 +2010,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
@@ -1988,14 +2022,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C12,C18:C20,C26:C26)</f>
-        <v>16.7333333333333</v>
+        <v>16.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2028,7 +2062,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -2039,118 +2073,118 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>14.5</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>14</v>
-      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>14.2222222222222</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2161,40 +2195,40 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2215,19 +2249,19 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C15:C20)</f>
-        <v>14.5</v>
+        <f>AVERAGE(C16:C20)</f>
+        <v>15.2</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -2248,10 +2282,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
@@ -2260,21 +2294,21 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C20,C26:C26)</f>
-        <v>14.6</v>
+        <f>AVERAGE(C2:C10,C16:C20,C26:C26)</f>
+        <v>14.6666666666667</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C12 C32" formulaRange="1"/>
+    <ignoredError sqref="C32 C13" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>